--- a/SLR/Full-Paper-Read/Paper-Review/PS20.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS20.xlsx
@@ -11,8 +11,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="I2">
+      <text>
+        <t xml:space="preserve">The paper presents the results of using the Systematic Reviews and Meta-Analyses (PRISMA) protocol. The topic is digital transformation and innovation on business ecosystems. The paper is not much relevant for CPS and SECO.
+	-Adnan Ashraf</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>ID</t>
   </si>
@@ -26,98 +42,50 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The paper presents the Python package PSY-TaLiRo (Python SYstems’ TemporAl LogIc RObustness) which is a toolbox for temporal logic robustness guided falsification of Cyber-Physical Systems (CPS). PSY-TaLiRo is a completely modular toolbox supporting multiple temporal logic offline monitors as well as optimization engines for test case generation.</t>
+    <t xml:space="preserve">This research aims to provide an ecosystem-inspired approach to digital transformation (DT) for sustainable innovations by reviewing the state-of-the-art research. The proposed innovation roadmap outlines the usefulness of the concept of “ecosystem innovation,” integrating the natural ecosystem, ecosystem services, ecosystem economy, business ecosystem, innovation ecosystem, and digital ecosystems, thereby calling for the eco-design of DT strategies that foster alignment and partnership across sectors and disciplines.
+The proposed roadmap puts Digital Ecosystems and IE into the central intersection of the Triple Helix model (of University-Industry- Government interaction), surrounding by (in order from the innermost) Business Ecosistems, Ecosystem Economy, Ecosystem Services, and Natural Ecosystem. </t>
+  </si>
+  <si>
+    <t>It does not concern CPS</t>
+  </si>
+  <si>
+    <t>CPS Case Study / Example availability</t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>CPS Case Study / Example availability</t>
-  </si>
-  <si>
-    <t>PSY-TaLiRo includes as Python demo an instance of the AircraftODE benchmark as well as the test setup scripts for the Python version of the F16 GCAS benchmark problem</t>
-  </si>
-  <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ1?</t>
+  </si>
+  <si>
+    <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
+  </si>
+  <si>
+    <t>It doesn't not propose methods, toolls or list benefits</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ2?</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
-      </rPr>
-      <t>https://gitlab.com/sbtg/pystaliro</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF000000"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
-      </rPr>
-      <t>https://sbtg.gitlab.io/pystaliro</t>
-    </r>
-  </si>
-  <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>Intelligence and automation</t>
-  </si>
-  <si>
-    <t>Continuous software and system engineering</t>
-  </si>
-  <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>A Python Toolbox for Search-Based Test Generation for Cyber-Physical Systems</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ1?</t>
-  </si>
-  <si>
-    <t>Partially</t>
-  </si>
-  <si>
-    <t>Temporal logic robustness guided falsification of CPS, multiple temporal logic offline monitors as well as optimization engines for test case generation</t>
-  </si>
-  <si>
-    <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>No mention of industry-academia collaboration.</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ2?</t>
+    <t>not sure</t>
   </si>
   <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
-  </si>
-  <si>
-    <t>Aerospace</t>
-  </si>
-  <si>
-    <t>Automotive</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
@@ -232,7 +200,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -258,13 +226,6 @@
       <name val="Arial"/>
     </font>
     <font/>
-    <font>
-      <i/>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -603,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -622,7 +583,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -636,126 +597,114 @@
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="18" fillId="5" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1072,7 +1021,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1099,7 +1048,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1107,28 +1056,28 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>13</v>
+      <c r="D6" s="22" t="s">
+        <v>11</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1136,10 +1085,10 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -1147,26 +1096,26 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>9</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="23" t="s">
-        <v>21</v>
+      <c r="I8" s="27" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1174,18 +1123,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="23" t="s">
-        <v>21</v>
+      <c r="I9" s="29" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1193,28 +1142,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>11</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1222,30 +1171,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="32">
+        <v>19</v>
+      </c>
+      <c r="C11" s="31">
         <f>Quality!C29</f>
-        <v>5</v>
+        <v>8.518518519</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="33" t="s">
-        <v>5</v>
+      <c r="I11" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="34" t="s">
-        <v>27</v>
+      <c r="B14" s="32" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="34" t="s">
-        <v>28</v>
+      <c r="B15" s="32" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2282,13 +2231,11 @@
       <formula1>"n.a.,Y,N"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="I5"/>
-  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2307,362 +2254,362 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="33"/>
+      <c r="B1" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="41"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="42"/>
+      <c r="B3" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="42"/>
+      <c r="B4" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="42"/>
+      <c r="B5" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="42"/>
+      <c r="B6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C6" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="43"/>
+      <c r="B7" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="42">
+      <c r="C7" s="40">
         <v>1.0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="43"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="43"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="44"/>
-      <c r="B4" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="44"/>
-      <c r="B5" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="44"/>
-      <c r="B6" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="46"/>
-      <c r="B7" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="47">
+      <c r="D7" s="44">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="44">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>9.166666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="42"/>
+      <c r="B9" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="42"/>
+      <c r="B10" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42"/>
+      <c r="B11" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42"/>
+      <c r="B12" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42"/>
+      <c r="B13" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42"/>
+      <c r="B14" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="C14" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42"/>
+      <c r="B15" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="44"/>
-      <c r="B9" s="49" t="s">
+      <c r="C15" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="42"/>
+      <c r="B16" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="44"/>
-      <c r="B10" s="49" t="s">
+      <c r="C16" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="42"/>
+      <c r="B17" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44"/>
-      <c r="B11" s="49" t="s">
+      <c r="C17" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42"/>
+      <c r="B18" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="49" t="s">
+      <c r="C18" s="47">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="43"/>
+      <c r="B19" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="44"/>
-      <c r="B13" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="44"/>
-      <c r="B14" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="51">
+      <c r="C19" s="47">
         <v>1.0</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="44"/>
-      <c r="B15" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="44"/>
-      <c r="B16" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="44"/>
-      <c r="B18" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46"/>
-      <c r="B19" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="47">
+      <c r="D19" s="44">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="44">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>1.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="54">
+      <c r="A20" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42"/>
+      <c r="B21" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42"/>
+      <c r="B22" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42"/>
+      <c r="B23" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="41"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42"/>
+      <c r="B24" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="51">
         <v>1.0</v>
       </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="44"/>
-      <c r="B21" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="54">
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="41"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="43"/>
+      <c r="B25" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="51">
         <v>1.0</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="44"/>
-      <c r="B22" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="55">
-        <v>0.0</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="44"/>
-      <c r="B23" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="44"/>
-      <c r="B24" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="55">
-        <v>0.0</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="43"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="46"/>
-      <c r="B25" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="56">
+      <c r="D25" s="52">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="56">
+      <c r="E25" s="52">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="F25" s="43"/>
+        <v>4.166666667</v>
+      </c>
+      <c r="F25" s="41"/>
     </row>
     <row r="26">
-      <c r="A26" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="59">
+      <c r="A26" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="55">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="41"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42"/>
+      <c r="B27" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="56">
         <v>1.0</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="43"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="44"/>
-      <c r="B27" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="59">
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="41"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43"/>
+      <c r="B28" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="56">
         <v>1.0</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="43"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="46"/>
-      <c r="B28" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="60">
-        <v>0.5</v>
-      </c>
-      <c r="D28" s="56">
+      <c r="D28" s="52">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="56">
+      <c r="E28" s="52">
         <f>(SUM(C26:C28)/D28)*10</f>
         <v>8.333333333</v>
       </c>
-      <c r="F28" s="43"/>
+      <c r="F28" s="41"/>
     </row>
     <row r="29">
-      <c r="B29" s="61">
+      <c r="B29" s="57">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="61">
+      <c r="C29" s="57">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>5</v>
+        <v>8.518518519</v>
       </c>
     </row>
   </sheetData>
